--- a/售后Agent_Dify复刻包/评测/评测集_v1.2_1027.xlsx
+++ b/售后Agent_Dify复刻包/评测/评测集_v1.2_1027.xlsx
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K22" s="44" t="inlineStr">
         <is>
-          <t>不可退：签收 10.8 天超过 7 天无理由期；提示质量问题通道</t>
+          <t>查到订单后先问退货原因，本轮没有给出结论</t>
         </is>
       </c>
       <c r="L22" s="45" t="n">
@@ -2504,7 +2504,7 @@
       <c r="O22" s="45" t="n"/>
       <c r="P22" s="45" t="inlineStr">
         <is>
-          <t>买家只说"想退货"，Agent 直接按「无理由」判定，没有先问原因；结论正确</t>
+          <t>v1.2 单轮里先追问原因（和 v1.1 的 R18 同一类：用例只有一轮），按口径不算错；v1.1 时是直接按无理由判定。下一版改成两轮用例</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K24" s="44" t="inlineStr">
         <is>
-          <t>不可退：冷链商品不支持无理由；有质量问题可申请</t>
+          <t>查到订单后先问退货原因，本轮没有给出结论</t>
         </is>
       </c>
       <c r="L24" s="45" t="n">
@@ -2642,7 +2642,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="45" t="n"/>
-      <c r="P24" s="45" t="n"/>
+      <c r="P24" s="45" t="inlineStr">
+        <is>
+          <t>同 R03：单轮用例和"先追问"的指令冲突，按口径不算错；下一版改成两轮用例</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="42" customHeight="1" s="32">
       <c r="A25" s="40" t="inlineStr">
@@ -2833,14 +2837,14 @@
       </c>
       <c r="K27" s="44" t="inlineStr">
         <is>
-          <t>①查订单后问原因 ②问是否拆封 ③可退：无理由期内、未拆封，有运费险</t>
+          <t>①查订单后就按「无理由、拆封未知」调了判定工具，再问是否拆封 ②再次问拆封 ③可退：大促延长 15 天无理由期内、未拆封，有运费险</t>
         </is>
       </c>
       <c r="L27" s="45" t="n">
         <v>1</v>
       </c>
       <c r="M27" s="45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="45" t="n">
         <v>0</v>
@@ -2848,7 +2852,7 @@
       <c r="O27" s="45" t="n"/>
       <c r="P27" s="45" t="inlineStr">
         <is>
-          <t>信息齐了才调判定工具（第③轮 check_policy：无理由、未拆封）</t>
+          <t>v1.2 新问题：第①轮买家只说"想退货"，Agent 没问原因就按「无理由」调了 check_policy（opened=未知），违反"听不出就问"；最终结论正确，工具调用记 0</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3126,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="45" t="n"/>
-      <c r="P31" s="45" t="n"/>
+      <c r="P31" s="45" t="inlineStr">
+        <is>
+          <t>第①轮先问是收到时就裂了还是后来才发现（v1.2 指令已明确）</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="42" customHeight="1" s="32">
       <c r="A32" s="40" t="inlineStr">
@@ -3177,7 +3185,7 @@
       </c>
       <c r="K32" s="44" t="inlineStr">
         <is>
-          <t>①可补发赠品，要开箱照片，并确认补发内容 ②买家同意后建补发工单 TK1026010680</t>
+          <t>①可补发赠品，要开箱照片 ②买家同意后建补发工单 TK1026010680</t>
         </is>
       </c>
       <c r="L32" s="45" t="n">
@@ -3249,7 +3257,7 @@
       </c>
       <c r="K33" s="46" t="inlineStr">
         <is>
-          <t>①先问是收到时就破了还是后来发现 ②物流破损：补发或退款，要照片 ③买家选补发后建工单 TK1026604961</t>
+          <t>①先问是收到时就破了还是后来发现 ②物流破损：补发或退款，要外箱和破损照片 ③买家选补发后建工单 TK1026604961</t>
         </is>
       </c>
       <c r="L33" s="45" t="n">
@@ -3264,7 +3272,7 @@
       <c r="O33" s="45" t="n"/>
       <c r="P33" s="44" t="inlineStr">
         <is>
-          <t>第①轮这次追问了破损时间</t>
+          <t>第①轮追问了破损时间；补发工单在买家同意之后才建（buyer_confirmed：是）</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3508,7 @@
       </c>
       <c r="F37" s="43" t="inlineStr">
         <is>
-          <t>QY20261001011 凝珠想退，没拆封</t>
+          <t>① QY20261001011 凝珠想退，没拆封  ② 不想要了</t>
         </is>
       </c>
       <c r="G37" s="43" t="inlineStr">
@@ -3515,7 +3523,7 @@
       </c>
       <c r="I37" s="42" t="inlineStr">
         <is>
-          <t>不可办理：签收 22 天，已超过无理由期</t>
+          <t>①查订单后问退货原因 ②不可办理：签收 22 天，已超过无理由期</t>
         </is>
       </c>
       <c r="J37" s="42" t="inlineStr">
@@ -3525,7 +3533,7 @@
       </c>
       <c r="K37" s="44" t="inlineStr">
         <is>
-          <t>查到订单后先问退货原因，本轮没有给出结论</t>
+          <t>①查到订单后问退货原因 ②不可退：签收 22 天，超过 7 天无理由期；提示质量问题通道</t>
         </is>
       </c>
       <c r="L37" s="45" t="n">
@@ -3540,7 +3548,7 @@
       <c r="O37" s="45" t="n"/>
       <c r="P37" s="45" t="inlineStr">
         <is>
-          <t>买家没说原因，按指令先追问，不算错；但这是单轮用例，期望的"不可办理"没出现。建议改成两轮用例（第②轮补"不想要了"）</t>
+          <t>v1.1 是单轮用例，Agent 按指令先追问原因，拿不到期望结论；v1.2 改成两轮用例，第②轮补"不想要了"</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3807,7 @@
       </c>
       <c r="K41" s="44" t="inlineStr">
         <is>
-          <t>致歉 + 转人工（工单 TK1026903940），未承诺任何金额</t>
+          <t>致歉 + 转人工（工单 TK1026550808），未承诺任何金额</t>
         </is>
       </c>
       <c r="L41" s="45" t="n">
@@ -3812,7 +3820,7 @@
       <c r="O41" s="45" t="n"/>
       <c r="P41" s="45" t="inlineStr">
         <is>
-          <t>工单号和 C03 相同（已知问题：没有订单号时工单号重复）</t>
+          <t>v1.1 时工单号和 C03 相同（都是 TK1026903940）；v1.2 没有订单号时把买家 ID 算进工单号，已不再重复</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3877,7 @@
       </c>
       <c r="K42" s="44" t="inlineStr">
         <is>
-          <t>直接转接人工（工单 TK1026903940），没有致歉</t>
+          <t>直接转接人工（工单 TK1026461435），没有致歉</t>
         </is>
       </c>
       <c r="L42" s="45" t="n">
@@ -3882,7 +3890,7 @@
       <c r="O42" s="45" t="n"/>
       <c r="P42" s="44" t="inlineStr">
         <is>
-          <t>工单号和 C02 相同</t>
+          <t>工单号和 C02 不再相同（v1.2 修复）</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3947,7 @@
       </c>
       <c r="K43" s="44" t="inlineStr">
         <is>
-          <t>①可退：无理由期内、有运费险 ②致歉 + 转人工，没答应红包</t>
+          <t>①可退：大促延长无理由期内、有运费险 ②致歉 + 转人工（工单 TK1026713096），没答应红包</t>
         </is>
       </c>
       <c r="L43" s="45" t="n">
@@ -4479,11 +4487,11 @@
       </c>
       <c r="K51" s="44" t="inlineStr">
         <is>
-          <t>走到 Agent，只要订单号，没有说明本店是清屿、元养订单要去元养店</t>
+          <t>说明本店是清屿官方旗舰店，元养的益生菌请到元养官方旗舰店处理；没有索要订单号，没有调工具</t>
         </is>
       </c>
       <c r="L51" s="45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="45" t="n">
         <v>1</v>
@@ -4491,14 +4499,10 @@
       <c r="N51" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="O51" s="44" t="inlineStr">
-        <is>
-          <t>知识或规则错</t>
-        </is>
-      </c>
+      <c r="O51" s="44" t="n"/>
       <c r="P51" s="46" t="inlineStr">
         <is>
-          <t>跨店铺识别规则只写在兜底回复 L 的提示词里，Agent 指令里没有</t>
+          <t>v1.1 失败（Agent 只要订单号）→ v1.2 指令加了第 1 步跨店铺识别；回归时连跑 3 次都通过</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="31" min="1" max="1"/>
@@ -4987,7 +4991,7 @@
     <col width="18" customWidth="1" style="31" min="3" max="3"/>
     <col width="40" customWidth="1" style="31" min="4" max="4"/>
     <col width="28" customWidth="1" style="31" min="5" max="5"/>
-    <col width="12" customWidth="1" style="31" min="6" max="6"/>
+    <col width="26" customWidth="1" style="31" min="6" max="6"/>
     <col width="14" customWidth="1" style="31" min="7" max="7"/>
     <col width="10" customWidth="1" style="31" min="8" max="8"/>
     <col width="44" customWidth="1" style="31" min="9" max="9"/>
@@ -5003,7 +5007,7 @@
     <row r="2" ht="15" customHeight="1" s="32">
       <c r="A2" s="53" t="inlineStr">
         <is>
-          <t>每次改动 Dify 后重跑评测，在这里记一行。v1.0、v1.1 没有保留逐条标注，指标留空；v1.2 的指标直接引用「汇总」页。</t>
+          <t>每次改动 Dify 后重跑评测，在这里记一行。「评测集」页保存的是最新一轮（v1.2，2026-10-29 实测）的逐条标注，v1.2 的指标直接引用「汇总」页；v1.0、v1.1 的指标是当轮跑完后记下的汇总数字。</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5058,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29.85" customHeight="1" s="32">
+    <row r="5" ht="78" customHeight="1" s="32">
       <c r="A5" s="61" t="inlineStr">
         <is>
           <t>v1.0</t>
@@ -5077,19 +5081,25 @@
       </c>
       <c r="E5" s="61" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="61" t="n"/>
-      <c r="G5" s="61" t="n"/>
-      <c r="H5" s="61" t="n"/>
+          <t>全部 50 条（首轮基线）</t>
+        </is>
+      </c>
+      <c r="F5" s="62" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G5" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="61" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" s="61" t="inlineStr">
         <is>
-          <t>投诉和普通转人工用的是同一套话术，买家只说"我要找人工"也会先致歉</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" s="32">
+          <t>任务完成 49/50；工具调用正确 25/25；越权 0 次。唯一失败是 C03：买家只说"我要找人工"，K 转人工也先说"非常抱歉给您带来不好的体验"——投诉和普通转人工用的是同一套话术</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="123" customHeight="1" s="32">
       <c r="A6" s="61" t="inlineStr">
         <is>
           <t>v1.1</t>
@@ -5112,19 +5122,25 @@
       </c>
       <c r="E6" s="61" t="inlineStr">
         <is>
-          <t>转人工相关用例</t>
-        </is>
-      </c>
-      <c r="F6" s="61" t="n"/>
-      <c r="G6" s="61" t="n"/>
-      <c r="H6" s="61" t="n"/>
+          <t>全部 50 条（用真实回复逐条跑并标注，多轮用例按网页预览的方式逐轮接着发）</t>
+        </is>
+      </c>
+      <c r="F6" s="62" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G6" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="61" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" s="61" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="32">
+          <t>任务完成 49/50；工具调用正确 25/25；越权 0 次。C03 已修复（直接转接，不再致歉）。唯一失败是 O05：买家问别家店的商品，Agent 没说明本店只处理清屿订单（v1.0 时这条是通过的，说明结果不稳定）。另外 C02、C03 工单号重复；R18 是单轮用例，Agent 按指令先追问原因，没在本轮给出结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="138" customHeight="1" s="32">
       <c r="A7" s="61" t="inlineStr">
         <is>
           <t>v1.2</t>
@@ -5132,22 +5148,22 @@
       </c>
       <c r="B7" s="61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C7" s="61" t="inlineStr">
         <is>
-          <t>v1.1（未改动）</t>
+          <t>v1.2 跨店识别 + 工单号修复</t>
         </is>
       </c>
       <c r="D7" s="61" t="inlineStr">
         <is>
-          <t>没有改 Dify；用真实回复把 50 条全部跑一遍并标注（多轮用例按网页预览的方式逐轮接着发）</t>
+          <t>① I 售后Agent 指令加第 1 步：买家问别家品牌的商品，说明本店只处理本店订单，请到对应旗舰店咨询，不要订单号、不调工具 ② 指令补破损追问：先问收到时就破了还是后来才发现 ③ K 转人工、after_sales：没有订单号时把买家 ID 算进工单号 ④ 评测集：R18 改成两轮用例</t>
         </is>
       </c>
       <c r="E7" s="61" t="inlineStr">
         <is>
-          <t>全部 50 条</t>
+          <t>全部 50 条（多轮用例逐轮带上一条消息 ID 接着发）；O05 连跑 3 次</t>
         </is>
       </c>
       <c r="F7" s="62">
@@ -5164,7 +5180,7 @@
       </c>
       <c r="I7" s="61" t="inlineStr">
         <is>
-          <t>任务完成 49/50；工具调用正确 25/25；越权 0 次。唯一失败是 O05：买家问别家店的商品，Agent 没说明本店只处理清屿订单。另外 C02、C03 工单号重复；R18 是单轮用例，Agent 按指令先追问原因，没在本轮给出结论</t>
+          <t>任务完成 50/50；工具调用正确 24/25；越权 0 次。O05 连跑 3 次都说明了本店只处理清屿订单；C02、C03 工单号不再重复；R18 第②轮给出"不可退"。新发现：R08 第①轮没问原因就按「无理由」调了判定工具（结论仍正确，工具调用记 0）；R03、R05 是单轮用例，Agent 先追问原因、本轮没给结论（和 v1.1 的 R18 同一类，按口径不算错）</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5221,16 @@
       </c>
       <c r="E10" s="65" t="inlineStr">
         <is>
+          <t>v1.1 状态</t>
+        </is>
+      </c>
+      <c r="F10" s="65" t="inlineStr">
+        <is>
           <t>v1.2 状态</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="58.2" customHeight="1" s="32">
+    <row r="11" ht="63" customHeight="1" s="32">
       <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Agent 认不出别家店铺的商品</t>
@@ -5235,8 +5256,13 @@
           <t>失败，需要修</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="58.2" customHeight="1" s="32">
+      <c r="F11" s="66" t="inlineStr">
+        <is>
+          <t>已修复：指令加了第 1 步跨店铺识别，回归时 O05 连跑 3 次都通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="63" customHeight="1" s="32">
       <c r="A12" s="57" t="inlineStr">
         <is>
           <t>破损类问题不追问就判定</t>
@@ -5262,8 +5288,13 @@
           <t>本轮没有出现（R12、R14 第①轮都先追问了），继续观察</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="29.85" customHeight="1" s="32">
+      <c r="F12" s="66" t="inlineStr">
+        <is>
+          <t>指令已明确破损先追问；R12、R14 第①轮都先问了收到时还是后来发现</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="63" customHeight="1" s="32">
       <c r="A13" s="57" t="inlineStr">
         <is>
           <t>没有订单号时工单号重复</t>
@@ -5289,8 +5320,13 @@
           <t>出现（C02、C03 都是 TK1026903940）</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="29.85" customHeight="1" s="32">
+      <c r="F13" s="66" t="inlineStr">
+        <is>
+          <t>已修复：C02 是 TK1026550808，C03 是 TK1026461435</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="33" customHeight="1" s="32">
       <c r="A14" s="57" t="inlineStr">
         <is>
           <t>同一用例两次结果不同</t>
@@ -5316,8 +5352,13 @@
           <t>回归时对不稳定用例多跑几次</t>
         </is>
       </c>
-    </row>
-    <row r="15">
+      <c r="F14" s="66" t="inlineStr">
+        <is>
+          <t>O05 连跑 3 次，3 次都通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="63" customHeight="1" s="32">
       <c r="A15" s="66" t="inlineStr">
         <is>
           <t>单轮用例和"先追问"的指令冲突</t>
@@ -5341,6 +5382,75 @@
       <c r="E15" s="66" t="inlineStr">
         <is>
           <t>用例设计问题，不算 Agent 错</t>
+        </is>
+      </c>
+      <c r="F15" s="66" t="inlineStr">
+        <is>
+          <t>R18 已改成两轮用例，第②轮给出"不可退"，通过；但 R03、R05 出现了同一类问题（见下）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="78" customHeight="1" s="32">
+      <c r="A16" s="66" t="inlineStr">
+        <is>
+          <t>单轮用例里先追问原因，拿不到结论</t>
+        </is>
+      </c>
+      <c r="B16" s="66" t="inlineStr">
+        <is>
+          <t>R03、R05</t>
+        </is>
+      </c>
+      <c r="C16" s="66" t="inlineStr">
+        <is>
+          <t>买家只说"没拆封，想退"，没说原因；Agent 按指令先问原因，单轮里拿不到期望结论</t>
+        </is>
+      </c>
+      <c r="D16" s="66" t="inlineStr">
+        <is>
+          <t>和 R18 一样，把 R03、R05 改成两轮用例，第②轮补"不想要了"</t>
+        </is>
+      </c>
+      <c r="E16" s="66" t="inlineStr">
+        <is>
+          <t>没出现（v1.1 直接按无理由给了结论）</t>
+        </is>
+      </c>
+      <c r="F16" s="66" t="inlineStr">
+        <is>
+          <t>出现，用例设计问题，不算 Agent 错</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="93" customHeight="1" s="32">
+      <c r="A17" s="66" t="inlineStr">
+        <is>
+          <t>没问原因就调判定工具</t>
+        </is>
+      </c>
+      <c r="B17" s="66" t="inlineStr">
+        <is>
+          <t>R08 第①轮</t>
+        </is>
+      </c>
+      <c r="C17" s="66" t="inlineStr">
+        <is>
+          <t>买家只说"想退货"，Agent 自己按「无理由」、拆封「未知」调了 check_policy</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="inlineStr">
+        <is>
+          <t>指令第 4 步加反例：买家只说"想退"时先问原因，不要默认按无理由判定</t>
+        </is>
+      </c>
+      <c r="E17" s="66" t="inlineStr">
+        <is>
+          <t>没出现（第③轮信息齐了才调）</t>
+        </is>
+      </c>
+      <c r="F17" s="66" t="inlineStr">
+        <is>
+          <t>出现：结论正确但工具调用记 0，下一版修</t>
         </is>
       </c>
     </row>
